--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/Opstart_documenten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16586C5A-377B-42EF-86B9-3379F31DD4B2}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E53968A-A582-4AF8-9F17-15E7351F9912}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
@@ -784,7 +784,7 @@
       <c r="H5" s="10"/>
       <c r="I5" s="10">
         <f>('Werkelijke uren'!D62)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>22</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>96.25</v>
+        <v>99.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>96.25</v>
+        <v>99.25</v>
       </c>
     </row>
   </sheetData>
@@ -1447,6 +1447,9 @@
       <c r="B37">
         <v>35</v>
       </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38">
@@ -1574,7 +1577,7 @@
       </c>
       <c r="D62">
         <f>SUM(C33:C62)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
@@ -1787,7 +1790,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>96.25</v>
+        <v>99.25</v>
       </c>
     </row>
   </sheetData>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/Opstart_documenten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E53968A-A582-4AF8-9F17-15E7351F9912}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FE0E0FB-1E8E-46C2-9B64-4F2896E6678C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
@@ -784,7 +784,7 @@
       <c r="H5" s="10"/>
       <c r="I5" s="10">
         <f>('Werkelijke uren'!D62)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>22</v>
@@ -830,7 +830,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>99.25</v>
+        <v>101.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>99.25</v>
+        <v>101.25</v>
       </c>
     </row>
   </sheetData>
@@ -1455,6 +1455,9 @@
       <c r="B38">
         <v>36</v>
       </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39">
@@ -1577,7 +1580,7 @@
       </c>
       <c r="D62">
         <f>SUM(C33:C62)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
@@ -1790,7 +1793,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>99.25</v>
+        <v>101.25</v>
       </c>
     </row>
   </sheetData>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/Opstart_documenten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FE0E0FB-1E8E-46C2-9B64-4F2896E6678C}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF222FDC-71DC-407D-B41D-183807DF28F0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>Nr</t>
   </si>
@@ -163,6 +163,12 @@
   </si>
   <si>
     <t>Geschatte duur (uren)</t>
+  </si>
+  <si>
+    <t>er is rekening gehouden met de krokus en paasvakantie</t>
+  </si>
+  <si>
+    <t>+ 2 weken om zolder om te bouwen naar studeer ruimte</t>
   </si>
 </sst>
 </file>
@@ -294,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -332,6 +338,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -347,10 +354,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -640,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -746,7 +749,7 @@
         <v>45945</v>
       </c>
       <c r="E4" s="11">
-        <v>45987</v>
+        <v>46010</v>
       </c>
       <c r="F4" s="10">
         <v>45</v>
@@ -772,10 +775,10 @@
         <v>18</v>
       </c>
       <c r="D5" s="11">
-        <v>45988</v>
+        <v>46027</v>
       </c>
       <c r="E5" s="11">
-        <v>46029</v>
+        <v>46087</v>
       </c>
       <c r="F5" s="10">
         <v>27</v>
@@ -801,10 +804,10 @@
         <v>19</v>
       </c>
       <c r="D6" s="11">
-        <v>46030</v>
+        <v>46090</v>
       </c>
       <c r="E6" s="11">
-        <v>46071</v>
+        <v>46150</v>
       </c>
       <c r="F6" s="10">
         <v>50</v>
@@ -857,10 +860,10 @@
         <v>17</v>
       </c>
       <c r="D9" s="12">
-        <v>46071</v>
+        <v>46132</v>
       </c>
       <c r="E9" s="12">
-        <v>46105</v>
+        <v>46166</v>
       </c>
       <c r="F9" s="2">
         <f>SUM(F10:F15)</f>
@@ -884,10 +887,10 @@
         <v>18</v>
       </c>
       <c r="D10" s="11">
-        <v>46071</v>
+        <v>46132</v>
       </c>
       <c r="E10" s="11">
-        <v>46087</v>
+        <v>46136</v>
       </c>
       <c r="F10" s="10">
         <v>12</v>
@@ -910,10 +913,10 @@
         <v>18</v>
       </c>
       <c r="D11" s="11">
-        <v>46090</v>
+        <v>46139</v>
       </c>
       <c r="E11" s="11">
-        <v>46105</v>
+        <v>46143</v>
       </c>
       <c r="F11" s="10">
         <v>12</v>
@@ -936,10 +939,10 @@
         <v>19</v>
       </c>
       <c r="D12" s="11">
-        <v>46111</v>
+        <v>46146</v>
       </c>
       <c r="E12" s="11">
-        <v>46113</v>
+        <v>46146</v>
       </c>
       <c r="F12" s="10">
         <v>4</v>
@@ -959,8 +962,12 @@
       <c r="C13" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
+      <c r="D13" s="11">
+        <v>46147</v>
+      </c>
+      <c r="E13" s="11">
+        <v>46150</v>
+      </c>
       <c r="F13" s="10">
         <v>12</v>
       </c>
@@ -1007,7 +1014,7 @@
         <v>17</v>
       </c>
       <c r="D16" s="12">
-        <v>46119</v>
+        <v>46153</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>20</v>
@@ -1034,10 +1041,10 @@
         <v>18</v>
       </c>
       <c r="D17" s="11">
-        <v>46119</v>
+        <v>46153</v>
       </c>
       <c r="E17" s="11">
-        <v>46139</v>
+        <v>46161</v>
       </c>
       <c r="F17" s="10">
         <v>15</v>
@@ -1060,10 +1067,10 @@
         <v>18</v>
       </c>
       <c r="D18" s="11">
-        <v>46140</v>
+        <v>46162</v>
       </c>
       <c r="E18" s="11">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="F18" s="10">
         <v>15</v>
@@ -1086,10 +1093,10 @@
         <v>19</v>
       </c>
       <c r="D19" s="11">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="E19" s="11">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="F19" s="10">
         <v>10</v>
@@ -1142,6 +1149,16 @@
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
         <v>101.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="19" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f020cdb928d38096/Programmeren/Odisee/LevensLang_Leren/LLL-BartBrondeel-2526/Opstart_documenten/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{482E40B1-4C12-41F6-8D36-DD9DCD6004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF222FDC-71DC-407D-B41D-183807DF28F0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4C0028-3BDC-4D66-85FD-02D406499F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
@@ -332,13 +332,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="15" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -659,20 +659,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="17" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="17"/>
+      <c r="E1" s="18"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="17"/>
+      <c r="H1" s="18"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
@@ -787,7 +787,7 @@
       <c r="H5" s="10"/>
       <c r="I5" s="10">
         <f>('Werkelijke uren'!D62)</f>
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>22</v>
@@ -833,7 +833,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>101.25</v>
+        <v>115.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>101.25</v>
+        <v>115.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1157,7 +1157,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="17" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1480,36 +1480,57 @@
       <c r="B39">
         <v>37</v>
       </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40">
         <v>38</v>
       </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41">
         <v>39</v>
       </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42">
         <v>40</v>
       </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43">
         <v>41</v>
       </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44">
         <v>42</v>
       </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45">
         <v>43</v>
       </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46">
@@ -1597,7 +1618,7 @@
       </c>
       <c r="D62">
         <f>SUM(C33:C62)</f>
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
@@ -1810,7 +1831,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>101.25</v>
+        <v>115.25</v>
       </c>
     </row>
   </sheetData>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4C0028-3BDC-4D66-85FD-02D406499F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB1AE63-C8DD-410D-9210-385ED3C00685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
@@ -787,7 +787,7 @@
       <c r="H5" s="10"/>
       <c r="I5" s="10">
         <f>('Werkelijke uren'!D62)</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>22</v>
@@ -833,7 +833,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>115.25</v>
+        <v>121.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>115.25</v>
+        <v>121.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1536,16 +1536,25 @@
       <c r="B46">
         <v>44</v>
       </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47">
         <v>45</v>
       </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48">
         <v>46</v>
       </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49">
@@ -1618,7 +1627,7 @@
       </c>
       <c r="D62">
         <f>SUM(C33:C62)</f>
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
@@ -1831,7 +1840,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>115.25</v>
+        <v>121.25</v>
       </c>
     </row>
   </sheetData>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB1AE63-C8DD-410D-9210-385ED3C00685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A71782A-E7C3-4C64-BAAA-1626BDCB1E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
@@ -787,7 +787,7 @@
       <c r="H5" s="10"/>
       <c r="I5" s="10">
         <f>('Werkelijke uren'!D62)</f>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>22</v>
@@ -833,7 +833,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>121.25</v>
+        <v>127.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>121.25</v>
+        <v>127.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1560,26 +1560,41 @@
       <c r="B49">
         <v>47</v>
       </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50">
         <v>48</v>
       </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51">
         <v>49</v>
       </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52">
         <v>50</v>
       </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53">
         <v>51</v>
       </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B54">
@@ -1627,7 +1642,7 @@
       </c>
       <c r="D62">
         <f>SUM(C33:C62)</f>
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>121.25</v>
+        <v>127.25</v>
       </c>
     </row>
   </sheetData>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A71782A-E7C3-4C64-BAAA-1626BDCB1E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7734AC7B-87F7-46BB-BE17-1BB27D902E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -754,8 +754,12 @@
       <c r="F4" s="10">
         <v>45</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
+      <c r="G4" s="11">
+        <v>46118</v>
+      </c>
+      <c r="H4" s="11">
+        <v>46129</v>
+      </c>
       <c r="I4" s="10">
         <f>('Werkelijke uren'!D32)</f>
         <v>85.25</v>
@@ -783,11 +787,13 @@
       <c r="F5" s="10">
         <v>27</v>
       </c>
-      <c r="G5" s="10"/>
+      <c r="G5" s="11">
+        <v>46132</v>
+      </c>
       <c r="H5" s="10"/>
       <c r="I5" s="10">
         <f>('Werkelijke uren'!D62)</f>
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>22</v>
@@ -833,7 +839,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>127.25</v>
+        <v>137.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1148,7 +1154,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>127.25</v>
+        <v>137.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1593,28 +1599,40 @@
         <v>51</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B54">
         <v>52</v>
       </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>53</v>
       </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>54</v>
       </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>55</v>
       </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58">
@@ -1642,7 +1660,7 @@
       </c>
       <c r="D62">
         <f>SUM(C33:C62)</f>
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
@@ -1855,7 +1873,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>127.25</v>
+        <v>137.25</v>
       </c>
     </row>
   </sheetData>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7734AC7B-87F7-46BB-BE17-1BB27D902E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0057C676-D22C-43FB-8C0E-7F1686949FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -790,10 +790,12 @@
       <c r="G5" s="11">
         <v>46132</v>
       </c>
-      <c r="H5" s="10"/>
+      <c r="H5" s="11">
+        <v>46140</v>
+      </c>
       <c r="I5" s="10">
         <f>('Werkelijke uren'!D62)</f>
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>22</v>
@@ -818,7 +820,9 @@
       <c r="F6" s="10">
         <v>50</v>
       </c>
-      <c r="G6" s="10"/>
+      <c r="G6" s="11">
+        <v>46141</v>
+      </c>
       <c r="H6" s="10"/>
       <c r="I6" s="10">
         <f>('Werkelijke uren'!D102)</f>
@@ -839,7 +843,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>137.25</v>
+        <v>145.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1154,7 +1158,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>137.25</v>
+        <v>145.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1638,29 +1642,44 @@
       <c r="B58">
         <v>56</v>
       </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59">
         <v>57</v>
       </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60">
         <v>58</v>
       </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>59</v>
       </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62">
         <v>60</v>
       </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
       <c r="D62">
         <f>SUM(C33:C62)</f>
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
@@ -1873,7 +1892,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>137.25</v>
+        <v>145.25</v>
       </c>
     </row>
   </sheetData>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0057C676-D22C-43FB-8C0E-7F1686949FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67280757-51D0-4D8F-923B-4144D6FE4454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -826,7 +826,7 @@
       <c r="H6" s="10"/>
       <c r="I6" s="10">
         <f>('Werkelijke uren'!D102)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>23</v>
@@ -843,7 +843,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>145.25</v>
+        <v>153.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>145.25</v>
+        <v>153.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1686,88 +1686,100 @@
       <c r="B63">
         <v>61</v>
       </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64">
         <v>62</v>
       </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65">
         <v>63</v>
       </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66">
         <v>64</v>
       </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67">
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69">
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70">
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71">
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72">
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73">
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74">
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75">
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76">
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77">
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78">
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79">
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80">
         <v>78</v>
       </c>
@@ -1883,7 +1895,7 @@
       </c>
       <c r="D102">
         <f>SUM(C63:C102)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
@@ -1892,7 +1904,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>145.25</v>
+        <v>153.25</v>
       </c>
     </row>
   </sheetData>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67280757-51D0-4D8F-923B-4144D6FE4454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550814C3-C405-4B3F-9F97-D461B1773B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -826,7 +826,7 @@
       <c r="H6" s="10"/>
       <c r="I6" s="10">
         <f>('Werkelijke uren'!D102)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>23</v>
@@ -843,7 +843,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>153.25</v>
+        <v>161.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>153.25</v>
+        <v>161.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1718,21 +1718,33 @@
       <c r="B67">
         <v>65</v>
       </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>66</v>
       </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69">
         <v>67</v>
       </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70">
         <v>68</v>
       </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71">
@@ -1895,7 +1907,7 @@
       </c>
       <c r="D102">
         <f>SUM(C63:C102)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
@@ -1904,7 +1916,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>153.25</v>
+        <v>161.25</v>
       </c>
     </row>
   </sheetData>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550814C3-C405-4B3F-9F97-D461B1773B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACBD4AF-328D-4B09-BDEC-71E8D8A3AD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -826,7 +826,7 @@
       <c r="H6" s="10"/>
       <c r="I6" s="10">
         <f>('Werkelijke uren'!D102)</f>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>23</v>
@@ -843,7 +843,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>161.25</v>
+        <v>169.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -907,7 +907,9 @@
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
+      <c r="I10" s="10">
+        <v>4</v>
+      </c>
       <c r="J10" s="10" t="s">
         <v>24</v>
       </c>
@@ -997,7 +999,7 @@
       <c r="H14" s="10"/>
       <c r="I14" s="10">
         <f>SUM(I10:I13)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" s="10"/>
     </row>
@@ -1158,7 +1160,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>161.25</v>
+        <v>173.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1750,21 +1752,33 @@
       <c r="B71">
         <v>69</v>
       </c>
+      <c r="C71">
+        <v>2</v>
+      </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72">
         <v>70</v>
       </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73">
         <v>71</v>
       </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74">
         <v>72</v>
       </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75">
@@ -1907,7 +1921,7 @@
       </c>
       <c r="D102">
         <f>SUM(C63:C102)</f>
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
@@ -1916,7 +1930,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>161.25</v>
+        <v>169.25</v>
       </c>
     </row>
   </sheetData>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACBD4AF-328D-4B09-BDEC-71E8D8A3AD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFFA5A2B-41AF-420E-AD40-267677594B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -826,7 +826,7 @@
       <c r="H6" s="10"/>
       <c r="I6" s="10">
         <f>('Werkelijke uren'!D102)</f>
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>23</v>
@@ -843,7 +843,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>169.25</v>
+        <v>201.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -1061,9 +1061,13 @@
       <c r="F17" s="10">
         <v>15</v>
       </c>
-      <c r="G17" s="10"/>
+      <c r="G17" s="11">
+        <v>46142</v>
+      </c>
       <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
+      <c r="I17" s="10">
+        <v>3</v>
+      </c>
       <c r="J17" s="10" t="s">
         <v>37</v>
       </c>
@@ -1131,7 +1135,7 @@
       <c r="H20" s="10"/>
       <c r="I20" s="10">
         <f>SUM(I17:I19)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="10"/>
     </row>
@@ -1160,7 +1164,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I14,I20)</f>
-        <v>173.25</v>
+        <v>208.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1784,108 +1788,156 @@
       <c r="B75">
         <v>73</v>
       </c>
+      <c r="C75">
+        <v>2</v>
+      </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76">
         <v>74</v>
       </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77">
         <v>75</v>
       </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78">
         <v>76</v>
       </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79">
         <v>77</v>
       </c>
+      <c r="C79">
+        <v>2</v>
+      </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80">
         <v>78</v>
       </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81">
         <v>79</v>
       </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82">
         <v>80</v>
       </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83">
         <v>81</v>
       </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84">
         <v>82</v>
       </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85">
         <v>83</v>
       </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86">
         <v>84</v>
       </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87">
         <v>85</v>
       </c>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88">
         <v>86</v>
       </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89">
         <v>87</v>
       </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90">
         <v>88</v>
       </c>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92">
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93">
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94">
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95">
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96">
         <v>94</v>
       </c>
@@ -1921,7 +1973,7 @@
       </c>
       <c r="D102">
         <f>SUM(C63:C102)</f>
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
@@ -1930,7 +1982,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>169.25</v>
+        <v>201.25</v>
       </c>
     </row>
   </sheetData>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFFA5A2B-41AF-420E-AD40-267677594B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9FC04E-8CA9-4388-8EB5-3C47F9C77C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -879,7 +879,9 @@
         <f>SUM(F10:F15)</f>
         <v>40</v>
       </c>
-      <c r="G9" s="2"/>
+      <c r="G9" s="12">
+        <v>46156</v>
+      </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
@@ -905,7 +907,7 @@
       <c r="F10" s="10">
         <v>12</v>
       </c>
-      <c r="G10" s="10"/>
+      <c r="G10" s="11"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10">
         <v>4</v>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9FC04E-8CA9-4388-8EB5-3C47F9C77C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9F580F-9E13-46CC-9D1A-E872E12BA524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
@@ -823,10 +823,12 @@
       <c r="G6" s="11">
         <v>46141</v>
       </c>
-      <c r="H6" s="10"/>
+      <c r="H6" s="11">
+        <v>46157</v>
+      </c>
       <c r="I6" s="10">
         <f>('Werkelijke uren'!D102)</f>
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>23</v>
@@ -843,7 +845,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10">
         <f>('Werkelijke uren'!C103)</f>
-        <v>201.25</v>
+        <v>213.25</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -880,10 +882,12 @@
         <v>40</v>
       </c>
       <c r="G9" s="12">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="I9" s="2">
+        <v>16</v>
+      </c>
       <c r="J9" s="2" t="s">
         <v>21</v>
       </c>
@@ -1165,8 +1169,8 @@
         <v>36</v>
       </c>
       <c r="I22">
-        <f>SUM(I7,I14,I20)</f>
-        <v>208.25</v>
+        <f>SUM(I7,I9,I14,I20)</f>
+        <v>236.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1918,64 +1922,100 @@
       <c r="B91">
         <v>89</v>
       </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92">
         <v>90</v>
       </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93">
         <v>91</v>
       </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94">
         <v>92</v>
       </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95">
         <v>93</v>
       </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96">
         <v>94</v>
       </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B97">
         <v>95</v>
       </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
     </row>
     <row r="98" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B98">
         <v>96</v>
       </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B99">
         <v>97</v>
       </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B100">
         <v>98</v>
       </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
     </row>
     <row r="101" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B101">
         <v>99</v>
       </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
     </row>
     <row r="102" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B102">
         <v>100</v>
       </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
       <c r="D102">
         <f>SUM(C63:C102)</f>
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
@@ -1984,7 +2024,7 @@
       </c>
       <c r="C103">
         <f>SUM(C3:C102)</f>
-        <v>201.25</v>
+        <v>213.25</v>
       </c>
     </row>
   </sheetData>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9F580F-9E13-46CC-9D1A-E872E12BA524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B4EF4A-FCE2-489B-B792-2AC53CF763A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>21</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I9,I14,I20)</f>
-        <v>236.25</v>
+        <v>244.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B4EF4A-FCE2-489B-B792-2AC53CF763A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025CF71C-6629-4EB9-9B3F-C99ACB63E957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -886,7 +886,7 @@
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>21</v>
@@ -911,10 +911,14 @@
       <c r="F10" s="10">
         <v>12</v>
       </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="10"/>
+      <c r="G10" s="11">
+        <v>46168</v>
+      </c>
+      <c r="H10" s="11">
+        <v>46169</v>
+      </c>
       <c r="I10" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>24</v>
@@ -1005,7 +1009,7 @@
       <c r="H14" s="10"/>
       <c r="I14" s="10">
         <f>SUM(I10:I13)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J14" s="10"/>
     </row>
@@ -1170,7 +1174,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I9,I14,I20)</f>
-        <v>244.25</v>
+        <v>255.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025CF71C-6629-4EB9-9B3F-C99ACB63E957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69E28C4-2BBF-4C1D-AA52-0DB7F9DCCDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="46">
   <si>
     <t>Nr</t>
   </si>
@@ -169,6 +169,9 @@
   </si>
   <si>
     <t>+ 2 weken om zolder om te bouwen naar studeer ruimte</t>
+  </si>
+  <si>
+    <t>05/052026</t>
   </si>
 </sst>
 </file>
@@ -886,7 +889,7 @@
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>21</v>
@@ -918,7 +921,7 @@
         <v>46169</v>
       </c>
       <c r="I10" s="10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>24</v>
@@ -943,9 +946,15 @@
       <c r="F11" s="10">
         <v>12</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
+      <c r="G11" s="11">
+        <v>46169</v>
+      </c>
+      <c r="H11" s="11">
+        <v>46170</v>
+      </c>
+      <c r="I11" s="10">
+        <v>4</v>
+      </c>
       <c r="J11" s="10" t="s">
         <v>25</v>
       </c>
@@ -1009,7 +1018,7 @@
       <c r="H14" s="10"/>
       <c r="I14" s="10">
         <f>SUM(I10:I13)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J14" s="10"/>
     </row>
@@ -1074,9 +1083,11 @@
       <c r="G17" s="11">
         <v>46142</v>
       </c>
-      <c r="H17" s="10"/>
+      <c r="H17" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="I17" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>37</v>
@@ -1101,9 +1112,13 @@
       <c r="F18" s="10">
         <v>15</v>
       </c>
-      <c r="G18" s="10"/>
+      <c r="G18" s="11">
+        <v>46154</v>
+      </c>
       <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
+      <c r="I18" s="10">
+        <v>4</v>
+      </c>
       <c r="J18" s="10" t="s">
         <v>26</v>
       </c>
@@ -1145,7 +1160,7 @@
       <c r="H20" s="10"/>
       <c r="I20" s="10">
         <f>SUM(I17:I19)</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J20" s="10"/>
     </row>
@@ -1174,7 +1189,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I9,I14,I20)</f>
-        <v>255.25</v>
+        <v>272.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69E28C4-2BBF-4C1D-AA52-0DB7F9DCCDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0E2975-92CB-4AB6-A597-42870A689CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -889,7 +889,7 @@
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>21</v>
@@ -1002,9 +1002,15 @@
       <c r="F13" s="10">
         <v>12</v>
       </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
+      <c r="G13" s="11">
+        <v>46170</v>
+      </c>
+      <c r="H13" s="11">
+        <v>46171</v>
+      </c>
+      <c r="I13" s="10">
+        <v>4</v>
+      </c>
       <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1018,7 +1024,7 @@
       <c r="H14" s="10"/>
       <c r="I14" s="10">
         <f>SUM(I10:I13)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J14" s="10"/>
     </row>
@@ -1189,7 +1195,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I9,I14,I20)</f>
-        <v>272.25</v>
+        <v>280.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0E2975-92CB-4AB6-A597-42870A689CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4404C449-4AC5-4CC5-AB13-8891FCE7E93A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -889,7 +889,7 @@
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>21</v>
@@ -1121,9 +1121,11 @@
       <c r="G18" s="11">
         <v>46154</v>
       </c>
-      <c r="H18" s="10"/>
+      <c r="H18" s="11">
+        <v>46175</v>
+      </c>
       <c r="I18" s="10">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>26</v>
@@ -1148,7 +1150,9 @@
       <c r="F19" s="10">
         <v>10</v>
       </c>
-      <c r="G19" s="10"/>
+      <c r="G19" s="11">
+        <v>46176</v>
+      </c>
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
       <c r="J19" s="10" t="s">
@@ -1166,7 +1170,7 @@
       <c r="H20" s="10"/>
       <c r="I20" s="10">
         <f>SUM(I17:I19)</f>
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J20" s="10"/>
     </row>
@@ -1195,7 +1199,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I9,I14,I20)</f>
-        <v>280.25</v>
+        <v>309.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4404C449-4AC5-4CC5-AB13-8891FCE7E93A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286478FD-A93D-4AB9-85B8-9846975FCF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>Nr</t>
   </si>
@@ -169,9 +169,6 @@
   </si>
   <si>
     <t>+ 2 weken om zolder om te bouwen naar studeer ruimte</t>
-  </si>
-  <si>
-    <t>05/052026</t>
   </si>
 </sst>
 </file>
@@ -889,7 +886,7 @@
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>21</v>
@@ -1089,8 +1086,8 @@
       <c r="G17" s="11">
         <v>46142</v>
       </c>
-      <c r="H17" s="10" t="s">
-        <v>45</v>
+      <c r="H17" s="11">
+        <v>46147</v>
       </c>
       <c r="I17" s="10">
         <v>6</v>
@@ -1199,7 +1196,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I9,I14,I20)</f>
-        <v>309.25</v>
+        <v>329.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286478FD-A93D-4AB9-85B8-9846975FCF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF61D79-7AFC-4135-B789-87581E295252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
-    <sheet name="Werkelijke uren" sheetId="2" r:id="rId2"/>
+    <sheet name="GitHub Commits" sheetId="4" r:id="rId2"/>
+    <sheet name="Werkelijke uren" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="189">
   <si>
     <t>Nr</t>
   </si>
@@ -169,13 +170,448 @@
   </si>
   <si>
     <t>+ 2 weken om zolder om te bouwen naar studeer ruimte</t>
+  </si>
+  <si>
+    <t>Urenregistratie via GitHub Commits — Bart Brondeel | Graduaat Programmeren Odisee 2025-2026</t>
+  </si>
+  <si>
+    <t>Datum</t>
+  </si>
+  <si>
+    <t>Categorie</t>
+  </si>
+  <si>
+    <t>Uren</t>
+  </si>
+  <si>
+    <t>Omschrijving commit(s)</t>
+  </si>
+  <si>
+    <t>GitHub bewijs</t>
+  </si>
+  <si>
+    <t>Cursus 1</t>
+  </si>
+  <si>
+    <t>Dag 1 - Werken met variabelen</t>
+  </si>
+  <si>
+    <t>Dag 2 - Data types en string manipulatie</t>
+  </si>
+  <si>
+    <t>Dag 3 - Controlestroom en logische operatoren</t>
+  </si>
+  <si>
+    <t>Dag 4 - Random en lijsten</t>
+  </si>
+  <si>
+    <t>✓ commit aanwezig</t>
+  </si>
+  <si>
+    <t>Dag 5 - For loop + range</t>
+  </si>
+  <si>
+    <t>Dag 6 - While loops en fucties</t>
+  </si>
+  <si>
+    <t>Dag 7 - Hangman Game</t>
+  </si>
+  <si>
+    <t>Dag 9 - Dictionaries, Secret Auction</t>
+  </si>
+  <si>
+    <t>30/10/2025</t>
+  </si>
+  <si>
+    <t>Dag 10-11 - Functies, Calculator, Blackjack</t>
+  </si>
+  <si>
+    <t>31/10/2025</t>
+  </si>
+  <si>
+    <t>Dag 12 - Scope, actieplan update</t>
+  </si>
+  <si>
+    <t>01/11/2025</t>
+  </si>
+  <si>
+    <t>Dag 13-14 - Debugging, hoger-lager spel</t>
+  </si>
+  <si>
+    <t>02/11/2025</t>
+  </si>
+  <si>
+    <t>Dag 15 - Coffee Machine, actieplan update</t>
+  </si>
+  <si>
+    <t>03/11/2025</t>
+  </si>
+  <si>
+    <t>Dag 16 - OOP, packages, logbook update</t>
+  </si>
+  <si>
+    <t>28/11/2025</t>
+  </si>
+  <si>
+    <t>Update week 46-47-48 logs</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>Dag 18 - Tekenen, Turtle</t>
+  </si>
+  <si>
+    <t>03/12/2025</t>
+  </si>
+  <si>
+    <t>Dag 17 quiz game + dag 19 schildpaddenrace</t>
+  </si>
+  <si>
+    <t>05/12/2025</t>
+  </si>
+  <si>
+    <t>Dag 20-21 - Snake Game deel 1 &amp; 2</t>
+  </si>
+  <si>
+    <t>06/12/2025</t>
+  </si>
+  <si>
+    <t>Dag 22 - Pong Game</t>
+  </si>
+  <si>
+    <t>08/12/2025</t>
+  </si>
+  <si>
+    <t>Dag 23 - Turtlecrossing game</t>
+  </si>
+  <si>
+    <t>09/12/2025</t>
+  </si>
+  <si>
+    <t>Dag 24 - Bestanden lezen/schrijven</t>
+  </si>
+  <si>
+    <t>10/12/2025</t>
+  </si>
+  <si>
+    <t>Dag 25 - CSV + Pandas + US State Quiz</t>
+  </si>
+  <si>
+    <t>11/12/2025</t>
+  </si>
+  <si>
+    <t>Dag 26 - List &amp; dict comprehension</t>
+  </si>
+  <si>
+    <t>12/12/2025</t>
+  </si>
+  <si>
+    <t>Dag 27 - Tkinter GUI</t>
+  </si>
+  <si>
+    <t>15/12/2025</t>
+  </si>
+  <si>
+    <t>Dag 28-29 - BlokTimer, Password Generator</t>
+  </si>
+  <si>
+    <t>16/12/2025</t>
+  </si>
+  <si>
+    <t>Dag 30 - Errors, Exceptions, JSON</t>
+  </si>
+  <si>
+    <t>19/12/2025</t>
+  </si>
+  <si>
+    <t>Dag 31-34 - Flash Cards, Email, ISS API, Quizzler + logbook</t>
+  </si>
+  <si>
+    <t>23/12/2025</t>
+  </si>
+  <si>
+    <t>Dag 35 - Twilio SMS API</t>
+  </si>
+  <si>
+    <t>24/12/2025</t>
+  </si>
+  <si>
+    <t>Dag 36 - Stock News Monitoring</t>
+  </si>
+  <si>
+    <t>Herstart na computer crash - Dag 1-2 herhaling</t>
+  </si>
+  <si>
+    <t>Dag 3-6</t>
+  </si>
+  <si>
+    <t>Dag 7-10</t>
+  </si>
+  <si>
+    <t>Dag 11-12</t>
+  </si>
+  <si>
+    <t>Dag 13-16</t>
+  </si>
+  <si>
+    <t>Dag 17-18</t>
+  </si>
+  <si>
+    <t>Dag 19-22</t>
+  </si>
+  <si>
+    <t>Dag 23-26</t>
+  </si>
+  <si>
+    <t>Dag 27-28</t>
+  </si>
+  <si>
+    <t>Dag 29-32</t>
+  </si>
+  <si>
+    <t>Dag 33-34</t>
+  </si>
+  <si>
+    <t>Dag 35-36</t>
+  </si>
+  <si>
+    <t>20/04/2026</t>
+  </si>
+  <si>
+    <t>Dag 37-38  HTTP Requests, Get, Post, Put, Delete / Setup API  referenties en spreadsheet</t>
+  </si>
+  <si>
+    <t>21/04/2026</t>
+  </si>
+  <si>
+    <t>Dag 39-43 - Flight Deals App Dag 39 + mail uitbreiding op Dag 40, HTML deel 1 en 2 + CSS deel 1</t>
+  </si>
+  <si>
+    <t>22/04/2026</t>
+  </si>
+  <si>
+    <t>Dag 44-46 - CSS, Web Scraping, Playlist + actieplan</t>
+  </si>
+  <si>
+    <t>23/04/2026</t>
+  </si>
+  <si>
+    <t>Dag 47-49 - Price tracker, Selenium</t>
+  </si>
+  <si>
+    <t>24/04/2026</t>
+  </si>
+  <si>
+    <t>Dag 50-51 - Twitter bot en Tinder bot</t>
+  </si>
+  <si>
+    <t>27/04/2026</t>
+  </si>
+  <si>
+    <t>Dag 52-55 - Extra scraping oefeningen + actieplan</t>
+  </si>
+  <si>
+    <t>28/04/2026</t>
+  </si>
+  <si>
+    <t>Dag 56-60 - Flask</t>
+  </si>
+  <si>
+    <t>29/04/2026</t>
+  </si>
+  <si>
+    <t>Dag 61-64 - Flask part 2 + actieplan</t>
+  </si>
+  <si>
+    <t>30/04/2026</t>
+  </si>
+  <si>
+    <t>Dag 65-68 - Web design / Authenntication with flask</t>
+  </si>
+  <si>
+    <t>Eindwerk</t>
+  </si>
+  <si>
+    <t>Eindwerk Sessie 1: Project setup - Flask Hello World</t>
+  </si>
+  <si>
+    <t>04/05/2026</t>
+  </si>
+  <si>
+    <t>Dag 69 - Blog part 4</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
+    <t>Dag 70-72 - Git, Github, Data exploration + actieplan</t>
+  </si>
+  <si>
+    <t>06/05/2026</t>
+  </si>
+  <si>
+    <t>Dag 73-74 - Data visualisatie</t>
+  </si>
+  <si>
+    <t>07/05/2026</t>
+  </si>
+  <si>
+    <t>Dag 75-78 - Data resampling, N-dim arrays</t>
+  </si>
+  <si>
+    <t>Dag 79-80 - Analysing / Tests / Distribution</t>
+  </si>
+  <si>
+    <t>Dag 81-84 - further practice the material we have covered</t>
+  </si>
+  <si>
+    <t>Dag 85-88 - further practice the material we have covered</t>
+  </si>
+  <si>
+    <t>Eindwerk: Sessie 2: Config klasse - OOP + python-dotenv</t>
+  </si>
+  <si>
+    <t>Dag 89-92 - further practice the material we have covered</t>
+  </si>
+  <si>
+    <t>Dag 93-96 - further practice the material we have covered</t>
+  </si>
+  <si>
+    <t>15/05/2026</t>
+  </si>
+  <si>
+    <t>Dag 97-100 - further practice the material we have covered</t>
+  </si>
+  <si>
+    <t>18/05/2026</t>
+  </si>
+  <si>
+    <t>Cursus 2</t>
+  </si>
+  <si>
+    <t>Cursus 2 Dag 1-4 - First Steps: Capturing and Storing User Input (Variabels, User Input, Lists)</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>Cursus 2 Dag 5-8 - Display and Structure Output (Enumeration, f-strings)</t>
+  </si>
+  <si>
+    <t>20/05/2026</t>
+  </si>
+  <si>
+    <t>Eindwerk: Sessie 3: HomeWizardMeter klasse</t>
+  </si>
+  <si>
+    <t>21/05/2026</t>
+  </si>
+  <si>
+    <t>Cursus 2 Dag 9-11 - Decision Making in Apps (If / Elif / Else / Dictionaries)</t>
+  </si>
+  <si>
+    <t>Eindwerk Sessie 4: PriceCalculator klasse</t>
+  </si>
+  <si>
+    <t>26/05/2026</t>
+  </si>
+  <si>
+    <t>Cursus 2 Dag 12-15 - Supercharge Functions with Arguments (Function Arguments, Defaults)</t>
+  </si>
+  <si>
+    <t>27/05/2026</t>
+  </si>
+  <si>
+    <t>Cursus 2 Dag 16-19 - Expand with External Libraries (Third-Party Modules, GitHub)</t>
+  </si>
+  <si>
+    <t>28/05/2026</t>
+  </si>
+  <si>
+    <t>Cursus 2 Dag 20-24 - Summary of Python Basics</t>
+  </si>
+  <si>
+    <t>29/05/2026</t>
+  </si>
+  <si>
+    <t>Cursus 2 Dag 25-28 - Build An AI Agent with Python and LangChain V1</t>
+  </si>
+  <si>
+    <t>Eindwerk Sessie 5: DataManager klasse</t>
+  </si>
+  <si>
+    <t>30/05/2026</t>
+  </si>
+  <si>
+    <t>Eindwerk Sessie 6: FluviusImporter klasse</t>
+  </si>
+  <si>
+    <t>01/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cursus 2 Dag 30-33 - Build a Weather Forecast Dashboard </t>
+  </si>
+  <si>
+    <t>02/06/2026</t>
+  </si>
+  <si>
+    <t>Cursus 2 Dag 34-39 - Build a Webcam Motion Alert App (Part 2: Email Alerting System)</t>
+  </si>
+  <si>
+    <t>Eindwerk Sessie 7: EntsoEApi klasse</t>
+  </si>
+  <si>
+    <t>03/06/2026</t>
+  </si>
+  <si>
+    <t>Cursus 2 Dag 40-45 - Hotel Booking System with OOP (Part 3: Various Method Types)</t>
+  </si>
+  <si>
+    <t>04/06/2026</t>
+  </si>
+  <si>
+    <t>Cursus 2 Dag 46-48 - Web Automation with Selenium in a GUI</t>
+  </si>
+  <si>
+    <t>05/06/2026</t>
+  </si>
+  <si>
+    <t>Cursus 2 Dag 49-51 - Django Web App (Part 1: Setup &amp; Models)</t>
+  </si>
+  <si>
+    <t>Eindwerk Sessie 8: Frontend dashboard</t>
+  </si>
+  <si>
+    <t>Eindwerk Sessie 9: Uitbreidingen + Foutafhandeling + Logging</t>
+  </si>
+  <si>
+    <t>08/06/2026</t>
+  </si>
+  <si>
+    <t>Cursus 2 Dag 52-56 - Django, ML + Restaurant Menu App</t>
+  </si>
+  <si>
+    <t>Totaal uren</t>
+  </si>
+  <si>
+    <t>TOTAAL</t>
+  </si>
+  <si>
+    <t>Alle categorieën</t>
+  </si>
+  <si>
+    <t>Totaal studeeruren bewezen via GitHub commits</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0\ &quot;u&quot;"/>
+  </numFmts>
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,8 +654,54 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0000CC"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1A7A1A"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -244,8 +726,33 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E4057"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF048A81"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDEBD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5F5E3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -296,11 +803,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -338,6 +860,100 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -886,7 +1502,7 @@
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>21</v>
@@ -975,9 +1591,15 @@
       <c r="F12" s="10">
         <v>4</v>
       </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
+      <c r="G12" s="11">
+        <v>46168</v>
+      </c>
+      <c r="H12" s="11">
+        <v>46181</v>
+      </c>
+      <c r="I12" s="10">
+        <v>6</v>
+      </c>
       <c r="J12" s="10"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1021,7 +1643,7 @@
       <c r="H14" s="10"/>
       <c r="I14" s="10">
         <f>SUM(I10:I13)</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J14" s="10"/>
     </row>
@@ -1090,7 +1712,7 @@
         <v>46147</v>
       </c>
       <c r="I17" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>37</v>
@@ -1122,7 +1744,7 @@
         <v>46175</v>
       </c>
       <c r="I18" s="10">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>26</v>
@@ -1151,7 +1773,9 @@
         <v>46176</v>
       </c>
       <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
+      <c r="I19" s="10">
+        <v>4</v>
+      </c>
       <c r="J19" s="10" t="s">
         <v>27</v>
       </c>
@@ -1167,7 +1791,7 @@
       <c r="H20" s="10"/>
       <c r="I20" s="10">
         <f>SUM(I17:I19)</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J20" s="10"/>
     </row>
@@ -1196,7 +1820,7 @@
       </c>
       <c r="I22">
         <f>SUM(I7,I9,I14,I20)</f>
-        <v>329.25</v>
+        <v>334.25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1220,6 +1844,1477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5312762-2708-4447-BD84-26DB3A26551F}">
+  <dimension ref="A1:E88"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="87.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+    </row>
+    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="23">
+        <v>45947</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="25">
+        <v>2</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="27"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="23">
+        <v>45950</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="25">
+        <v>2</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="27"/>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="23">
+        <v>45951</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="25">
+        <v>2</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="27"/>
+    </row>
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="23">
+        <v>45952</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="25">
+        <v>2</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="23">
+        <v>45953</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="25">
+        <v>2</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="23">
+        <v>45954</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="25">
+        <v>2</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="23">
+        <v>45957</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="25">
+        <v>3</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="23">
+        <v>45958</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="25">
+        <v>2</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="25">
+        <v>4</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="25">
+        <v>2</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="25">
+        <v>4</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="25">
+        <v>2</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="25">
+        <v>2</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="25">
+        <v>2</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="25">
+        <v>2</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="25">
+        <v>4</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="25">
+        <v>2</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="25">
+        <v>2</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="25">
+        <v>2</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="25">
+        <v>2</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="25">
+        <v>2</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="25">
+        <v>2</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="25">
+        <v>2</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="25">
+        <v>2</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="25">
+        <v>2</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="25">
+        <v>2</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="25">
+        <v>2</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="25">
+        <v>2</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="23">
+        <v>46114</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="25">
+        <v>5</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="23">
+        <v>46115</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="25">
+        <v>5</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="23">
+        <v>46118</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="25">
+        <v>5</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="23">
+        <v>46119</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="25">
+        <v>2</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="23">
+        <v>46120</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="25">
+        <v>6</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="23">
+        <v>46121</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="25">
+        <v>3</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="E36" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="23">
+        <v>46122</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="25">
+        <v>6</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="23">
+        <v>46125</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="25">
+        <v>6</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E38" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="23">
+        <v>46126</v>
+      </c>
+      <c r="B39" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="25">
+        <v>2</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E39" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="23">
+        <v>46127</v>
+      </c>
+      <c r="B40" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="25">
+        <v>6</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="E40" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="23">
+        <v>46128</v>
+      </c>
+      <c r="B41" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="25">
+        <v>2</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="E41" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="23">
+        <v>46129</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="25">
+        <v>2</v>
+      </c>
+      <c r="D42" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="E42" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" s="25">
+        <v>4</v>
+      </c>
+      <c r="D43" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="E43" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" s="25">
+        <v>9</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="E44" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="B45" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="25">
+        <v>5</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B46" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="25">
+        <v>5</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="E46" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="25">
+        <v>2</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B48" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="25">
+        <v>8</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" s="25">
+        <v>9</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" s="25">
+        <v>7</v>
+      </c>
+      <c r="D50" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E50" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" s="25">
+        <v>7</v>
+      </c>
+      <c r="D51" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="B52" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C52" s="31">
+        <v>2</v>
+      </c>
+      <c r="D52" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="E52" s="32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="B53" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C53" s="25">
+        <v>2</v>
+      </c>
+      <c r="D53" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C54" s="25">
+        <v>6</v>
+      </c>
+      <c r="D54" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="B55" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" s="25">
+        <v>4</v>
+      </c>
+      <c r="D55" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="B56" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C56" s="25">
+        <v>9</v>
+      </c>
+      <c r="D56" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="23">
+        <v>46150</v>
+      </c>
+      <c r="B57" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C57" s="25">
+        <v>4</v>
+      </c>
+      <c r="D57" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="E57" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="23">
+        <v>46153</v>
+      </c>
+      <c r="B58" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C58" s="25">
+        <v>7</v>
+      </c>
+      <c r="D58" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="E58" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="23">
+        <v>46154</v>
+      </c>
+      <c r="B59" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C59" s="25">
+        <v>7</v>
+      </c>
+      <c r="D59" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="E59" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="33">
+        <v>46154</v>
+      </c>
+      <c r="B60" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60" s="31">
+        <v>2</v>
+      </c>
+      <c r="D60" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="E60" s="32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="23">
+        <v>46155</v>
+      </c>
+      <c r="B61" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C61" s="25">
+        <v>8</v>
+      </c>
+      <c r="D61" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="E61" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="23">
+        <v>46156</v>
+      </c>
+      <c r="B62" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C62" s="25">
+        <v>7</v>
+      </c>
+      <c r="D62" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="E62" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="B63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C63" s="25">
+        <v>7</v>
+      </c>
+      <c r="D63" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="E63" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="B64" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C64" s="36">
+        <v>7</v>
+      </c>
+      <c r="D64" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="E64" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="B65" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C65" s="36">
+        <v>2</v>
+      </c>
+      <c r="D65" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="B66" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C66" s="31">
+        <v>2</v>
+      </c>
+      <c r="D66" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="E66" s="32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="B67" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C67" s="36">
+        <v>5</v>
+      </c>
+      <c r="D67" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="B68" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C68" s="31">
+        <v>2</v>
+      </c>
+      <c r="D68" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="E68" s="32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="B69" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C69" s="36">
+        <v>6</v>
+      </c>
+      <c r="D69" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="E69" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="B70" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C70" s="36">
+        <v>9</v>
+      </c>
+      <c r="D70" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="E70" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="B71" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C71" s="36">
+        <v>8</v>
+      </c>
+      <c r="D71" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="E71" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="B72" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C72" s="36">
+        <v>8</v>
+      </c>
+      <c r="D72" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="E72" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="B73" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C73" s="31">
+        <v>2</v>
+      </c>
+      <c r="D73" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="E73" s="32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="B74" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C74" s="31">
+        <v>2</v>
+      </c>
+      <c r="D74" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="E74" s="32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="B75" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C75" s="36">
+        <v>5</v>
+      </c>
+      <c r="D75" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="E75" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="B76" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" s="36">
+        <v>7</v>
+      </c>
+      <c r="D76" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="E76" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="B77" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C77" s="31">
+        <v>2</v>
+      </c>
+      <c r="D77" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="E77" s="32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="B78" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C78" s="36">
+        <v>9</v>
+      </c>
+      <c r="D78" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="E78" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="B79" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C79" s="36">
+        <v>5</v>
+      </c>
+      <c r="D79" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="E79" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="B80" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C80" s="36">
+        <v>2</v>
+      </c>
+      <c r="D80" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="E80" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="B81" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C81" s="31">
+        <v>2</v>
+      </c>
+      <c r="D81" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="E81" s="32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="33">
+        <v>46181</v>
+      </c>
+      <c r="B82" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C82" s="31">
+        <v>2</v>
+      </c>
+      <c r="D82" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="E82" s="32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="B83" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C83" s="36">
+        <v>6</v>
+      </c>
+      <c r="D83" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="E83" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="B85" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="C85" s="40">
+        <f>SUMIF(B11:B83,"Cursus 1",C11:C83)</f>
+        <v>213</v>
+      </c>
+      <c r="D85" s="41"/>
+      <c r="E85" s="26"/>
+    </row>
+    <row r="86" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="B86" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="C86" s="44">
+        <f>SUMIF(B11:B83,"Cursus 2",C11:C83)</f>
+        <v>79</v>
+      </c>
+      <c r="D86" s="45"/>
+      <c r="E86" s="34"/>
+    </row>
+    <row r="87" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="B87" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="C87" s="48">
+        <f>SUMIF(B11:B83,"Eindwerk",C11:C83)</f>
+        <v>18</v>
+      </c>
+      <c r="D87" s="49"/>
+      <c r="E87" s="29"/>
+    </row>
+    <row r="88" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="B88" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="C88" s="51">
+        <f>C85+C86+C87</f>
+        <v>310</v>
+      </c>
+      <c r="D88" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="E88" s="50"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3793691-12BB-4C09-897D-D3E0C91FA681}">
   <dimension ref="B2:D103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Opstart_documenten/Actieplan_Python.xlsx
+++ b/Opstart_documenten/Actieplan_Python.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Odisee\LLL-BartBrondeel-2526\Opstart_documenten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF61D79-7AFC-4135-B789-87581E295252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F805A10-EE3B-4651-B918-225697E7963E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actieplan" sheetId="1" r:id="rId1"/>
